--- a/workflows/cul-01-vision-purpose/trackers/CUL-01_Vision_OKR_Tracker.xlsx
+++ b/workflows/cul-01-vision-purpose/trackers/CUL-01_Vision_OKR_Tracker.xlsx
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Robert McCarthy</t>
+          <t>Robert T. McCarthy</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
